--- a/frontend/public/Sample_VDS_Format.xlsx
+++ b/frontend/public/Sample_VDS_Format.xlsx
@@ -6245,12 +6245,6 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="I5" s="68">
-        <f>SUM(I4:I4)</f>
-        <v>1085</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A3:J3" xr:uid="{00000000-0009-0000-0000-000014000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:J23">
